--- a/Schemas/Template_Schema.xlsx
+++ b/Schemas/Template_Schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvih\OneDrive\Documents\LearningCodeProjects\AuditNotesWebSite\Schemas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9E2E15-9D28-40A7-9791-4FF9674CAAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C889737C-2310-4BDE-89D5-74E6B07C995E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Item Number</t>
   </si>
@@ -58,6 +58,16 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>Instructions: 
+-First Column Item Number is Manadatory in each sheet
+- Add description of item in Title Column.Title can be renamed
+-If additional columns are required then add them after Item Number(mandatory column)
+-You can also add multiple sheets but each sheet must has Item Number column
+-Please make sure Item Number is unique and column data type is text
+-Once Schema files have been finalized and do not make changes in item numbers or tab names to avoid losing link to related Knowledge Base and Audit Notes
+-MOVE ALL SCHEMA FILES UNDER SCHEMA TEMPLATES/CUSTOM TAB</t>
   </si>
 </sst>
 </file>
@@ -457,12 +467,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="198" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
